--- a/poc/out/game.xlsx
+++ b/poc/out/game.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t xml:space="preserve">186611255334439cb6f933372565871b</t>
+          <t xml:space="preserve">a771c46accea41a5949541d0b947a01d</t>
         </is>
       </c>
       <c r="U4">
@@ -500,7 +500,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9f6cd90bd5fb4e4eb81e4256d051b686</t>
+          <t xml:space="preserve">2f44643850554b258586e60cb5bfa5d8</t>
         </is>
       </c>
       <c r="U5">
@@ -624,7 +624,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">cb70262644a64589a3caf459fe2ca39e</t>
+          <t xml:space="preserve">471ef896131f490ba5a5364871f32475</t>
         </is>
       </c>
       <c r="E4">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">e607c7cf148f4bebb8de39829daeb09e</t>
+          <t xml:space="preserve">70274bfbb0ae4d10aebf55becd2f38e4</t>
         </is>
       </c>
       <c r="E5">
@@ -666,7 +666,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0075a00484034c0b8b44010941f90298</t>
+          <t xml:space="preserve">3c6c162af37541a0bb37370b9cc2cc93</t>
         </is>
       </c>
       <c r="E6">
@@ -824,7 +824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ba002a4f5b304d93a3fd11a444a3a34b</t>
+          <t xml:space="preserve">6c6e0efa1b8d46358c91a6c185de9eea</t>
         </is>
       </c>
       <c r="G4">
@@ -855,7 +855,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2c546f3ec5f847d9a473d74b8530a9bd</t>
+          <t xml:space="preserve">64ab30dab07a42ef8592701cd5dc80a7</t>
         </is>
       </c>
       <c r="G5">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ebc75d03942648cabae54923fc3979e9</t>
+          <t xml:space="preserve">0dc7ac438ab943e9810e8efe66f9ea62</t>
         </is>
       </c>
       <c r="G4">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">87fa28685c344af4b8f0a1dfa691b4fc</t>
+          <t xml:space="preserve">4f047bcb9688415f92eba133b52eac21</t>
         </is>
       </c>
       <c r="G5">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">guid=c7c04a3b88c6459c94d4b3dcd0344063</t>
+          <t xml:space="preserve">guid=39579e7b442b4cbfb3bc0c9cb85bcce3</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">saved_utc=2026-07-09T12:46:24Z</t>
+          <t xml:space="preserve">saved_utc=2026-07-09T17:07:08Z</t>
         </is>
       </c>
     </row>
